--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512407_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512407_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.150399999999999</v>
+        <v>10.6696</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7081</v>
+        <v>8.869899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4424</v>
+        <v>1.7997</v>
       </c>
       <c r="G2" t="n">
-        <v>6.211</v>
+        <v>6.2988</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1924</v>
+        <v>0.1974</v>
       </c>
       <c r="I2" t="n">
-        <v>6.0185</v>
+        <v>6.1013</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4444</v>
+        <v>6.5778</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8898</v>
+        <v>0.9272</v>
       </c>
       <c r="L2" t="n">
-        <v>5.5547</v>
+        <v>5.6507</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2335</v>
+        <v>-0.2791</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6973</v>
+        <v>-0.7297</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0486</v>
+        <v>0.3967</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5073</v>
+        <v>0.5068</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5414</v>
+        <v>-0.1102</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3493</v>
+        <v>2.3546</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5784</v>
+        <v>0.5693</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0755</v>
+        <v>4.9862</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3262</v>
+        <v>4.5658</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7492</v>
+        <v>0.4204</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2763</v>
+        <v>2.3228</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8625</v>
+        <v>-0.4351</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4139</v>
+        <v>2.7579</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2343</v>
+        <v>2.5037</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5876</v>
+        <v>-0.0804</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6468</v>
+        <v>2.5841</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.958</v>
+        <v>-0.181</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7251</v>
+        <v>-0.3548</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2329</v>
+        <v>0.1738</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0485</v>
+        <v>1.0123</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1145</v>
+        <v>0.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1404</v>
+        <v>0.8719</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9741</v>
+        <v>-0.2919</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6846</v>
+        <v>1.0712</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6846</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7693</v>
+        <v>4.8427</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7271</v>
+        <v>2.485</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9579</v>
+        <v>2.3577</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0461</v>
+        <v>2.3141</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3223</v>
+        <v>1.8959</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7239</v>
+        <v>0.4182</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5077</v>
+        <v>3.3054</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2706</v>
+        <v>2.6458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2371</v>
+        <v>0.6596</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4615</v>
+        <v>-0.9913</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9483</v>
+        <v>-0.7499</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4868</v>
+        <v>-0.2414</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4097</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4339</v>
+        <v>2.0245</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7678</v>
+        <v>1.8661</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3369</v>
+        <v>1.2041</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4309</v>
+        <v>0.662</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4544</v>
+        <v>0.6625</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9068</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3612</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5465</v>
+        <v>4.5549</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2837</v>
+        <v>5.8629</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2628</v>
+        <v>-1.308</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3133</v>
+        <v>3.0577</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4403</v>
+        <v>2.3508</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7536</v>
+        <v>0.7069</v>
       </c>
       <c r="J5" t="n">
-        <v>2.463</v>
+        <v>3.5758</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1055</v>
+        <v>3.3373</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5685</v>
+        <v>0.2385</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1496</v>
+        <v>-0.518</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3348</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1852</v>
+        <v>0.4684</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1464</v>
+        <v>1.5297</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6401</v>
+        <v>1.3564</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4937</v>
+        <v>0.1733</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0625</v>
+        <v>-0.4374</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1806</v>
+        <v>1.943</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1181</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.91</v>
+        <v>3.2124</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6834</v>
+        <v>2.0332</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2267</v>
+        <v>1.1792</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1318</v>
+        <v>-0.7551</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5518999999999999</v>
+        <v>1.7187</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4202</v>
+        <v>-2.4738</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4033</v>
+        <v>0.4348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2848</v>
+        <v>3.1002</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1185</v>
+        <v>-2.6654</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5351</v>
+        <v>-1.19</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8367</v>
+        <v>-1.3815</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3016</v>
+        <v>0.1915</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4097</v>
+        <v>1.4172</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6388</v>
+        <v>2.4294</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4515</v>
+        <v>1.7043</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3285</v>
+        <v>1.1695</v>
       </c>
       <c r="U6" t="n">
-        <v>1.123</v>
+        <v>0.5349</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4485</v>
+        <v>2.8289</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6045</v>
+        <v>1.7659</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8441</v>
+        <v>1.0631</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1501</v>
+        <v>-3.1037</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1368</v>
+        <v>-1.1084</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0133</v>
+        <v>-1.9953</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7918</v>
+        <v>-1.6936</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2443</v>
+        <v>-0.1811</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5475</v>
+        <v>-1.5125</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3583</v>
+        <v>-1.4101</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5037</v>
+        <v>1.8154</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3127</v>
+        <v>1.3182</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1911</v>
+        <v>0.4972</v>
       </c>
       <c r="V7" t="n">
-        <v>3.8901</v>
+        <v>3.9148</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1321</v>
+        <v>4.1657</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3101</v>
+        <v>2.171</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4882</v>
+        <v>1.5811</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8218</v>
+        <v>0.5899</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7876</v>
+        <v>-1.7857</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6978</v>
+        <v>-0.8286</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4854</v>
+        <v>-0.957</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3429</v>
+        <v>-0.3755</v>
       </c>
       <c r="K8" t="n">
-        <v>3.0364</v>
+        <v>0.2371</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6935</v>
+        <v>-0.6126</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1305</v>
+        <v>-1.4101</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3386</v>
+        <v>-1.0657</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2081</v>
+        <v>-0.3444</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4339</v>
+        <v>1.8221</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4582</v>
+        <v>1.8221</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8314</v>
+        <v>0.2561</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7469</v>
+        <v>0.2646</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8324</v>
+        <v>1.8785</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4227</v>
+        <v>1.6921</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5903</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5751</v>
+        <v>1.589</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.2047</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9405</v>
+        <v>1.7937</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7418</v>
+        <v>-0.1396</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7977</v>
+        <v>-0.5534</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9442</v>
+        <v>0.4138</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3835</v>
+        <v>0.434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2342</v>
+        <v>0.3147</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6177</v>
+        <v>0.1193</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3583</v>
+        <v>-0.5736</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0318</v>
+        <v>-0.8682</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3264</v>
+        <v>0.2945</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8436</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8436</v>
+        <v>1.6196</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4038</v>
+        <v>2.1335</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6466</v>
+        <v>1.3858</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2428</v>
+        <v>0.7477</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8771</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6647</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6872</v>
+        <v>-0.4884</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1115</v>
+        <v>0.0993</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5758</v>
+        <v>-0.5877</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6872</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1756</v>
+        <v>-0.1778</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5183</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7068</v>
+        <v>-0.7158</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5183</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2048</v>
+        <v>0.0052</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.131</v>
+        <v>0.0796</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3846</v>
+        <v>-0.8747</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1258</v>
+        <v>0.2316</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5104</v>
+        <v>-1.1063</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1821</v>
+        <v>-0.6491</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1342</v>
+        <v>-0.6314</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0479</v>
+        <v>-0.0177</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1208</v>
+        <v>-0.4706</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5074</v>
+        <v>0.1185</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6282</v>
+        <v>-0.5891</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0612</v>
+        <v>-0.1785</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6415</v>
+        <v>-0.7499</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5803</v>
+        <v>0.5714</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6388</v>
+        <v>0.2025</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6388</v>
+        <v>1.2147</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4089</v>
+        <v>0.0351</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2466</v>
+        <v>0.2733</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1622</v>
+        <v>-0.2382</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.2502</v>
+        <v>-0.4632</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.2502</v>
+        <v>-1.9043</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4123</v>
+        <v>-0.9276</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4068</v>
+        <v>0.993</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0054</v>
+        <v>-1.9206</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6309</v>
+        <v>-0.1909</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.608</v>
+        <v>-0.157</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0229</v>
+        <v>-0.034</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4861</v>
+        <v>-0.0917</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1171</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6032</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1448</v>
+        <v>-0.0992</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7251</v>
+        <v>-0.6706</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5803</v>
+        <v>0.5714</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2048</v>
+        <v>1.6196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2291</v>
+        <v>1.6196</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5199</v>
+        <v>1.9285</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3191</v>
+        <v>1.0847</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2008</v>
+        <v>0.8437</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4663</v>
+        <v>-4.2847</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.889</v>
+        <v>-4.2847</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>32.3013</v>
+        <v>32.56400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>27.0633</v>
+        <v>28.283</v>
       </c>
       <c r="F13" t="n">
-        <v>5.238</v>
+        <v>4.281099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>6.535200000000003</v>
+        <v>6.6732</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2305</v>
+        <v>2.2711</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3048</v>
+        <v>4.402</v>
       </c>
       <c r="J13" t="n">
-        <v>13.6329</v>
+        <v>14.2199</v>
       </c>
       <c r="K13" t="n">
-        <v>10.5976</v>
+        <v>10.9527</v>
       </c>
       <c r="L13" t="n">
-        <v>3.0355</v>
+        <v>3.2673</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.097600000000002</v>
+        <v>-7.5467</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.366900000000001</v>
+        <v>-8.6815</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2695</v>
+        <v>1.1347</v>
       </c>
       <c r="P13" t="n">
-        <v>8.1937</v>
+        <v>8.0983</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.2181</v>
+        <v>-9.110400000000002</v>
       </c>
       <c r="R13" t="n">
-        <v>17.412</v>
+        <v>17.2085</v>
       </c>
       <c r="S13" t="n">
-        <v>12.0471</v>
+        <v>12.2506</v>
       </c>
       <c r="T13" t="n">
-        <v>9.148100000000001</v>
+        <v>9.514900000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8988</v>
+        <v>2.7357</v>
       </c>
       <c r="V13" t="n">
-        <v>5.525099999999999</v>
+        <v>5.542299999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>13.5005</v>
+        <v>13.6585</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.975500000000001</v>
+        <v>-8.116099999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1782</v>
+        <v>1.189</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1782</v>
+        <v>1.189</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1782</v>
+        <v>1.189</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5855</v>
+        <v>0.5926</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1782</v>
+        <v>1.189</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5855</v>
+        <v>0.5926</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9621</v>
+        <v>0.9254</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8382</v>
+        <v>3.3521</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8761</v>
+        <v>-2.4267</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9475</v>
+        <v>2.9561</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2147</v>
+        <v>0.2173</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7328</v>
+        <v>2.7387</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5484</v>
+        <v>3.6125</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8597</v>
+        <v>1.8958</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6887</v>
+        <v>1.7167</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6009</v>
+        <v>-0.6565</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6451</v>
+        <v>-1.6785</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0442</v>
+        <v>1.022</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2237</v>
+        <v>-1.2896</v>
       </c>
       <c r="T15" t="n">
-        <v>0.411</v>
+        <v>-0.1992</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6347</v>
+        <v>-1.0904</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2868</v>
+        <v>1.2834</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1627</v>
+        <v>0.4983</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3785</v>
+        <v>3.6857</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5412</v>
+        <v>-3.1874</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3426</v>
+        <v>-0.3501</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0171</v>
+        <v>0.0384</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3597</v>
+        <v>-0.3885</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6801</v>
+        <v>2.7484</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9689</v>
+        <v>2.0328</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7113</v>
+        <v>0.7156</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0227</v>
+        <v>-3.0984</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9518</v>
+        <v>-1.9943</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0709</v>
+        <v>-1.1041</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7829</v>
+        <v>-1.1031</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4822</v>
+        <v>-0.2529</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3007</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9385</v>
+        <v>0.9393</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6005</v>
+        <v>-0.8854</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0123</v>
+        <v>-0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6129</v>
+        <v>-0.7754</v>
       </c>
       <c r="G17" t="n">
-        <v>0.479</v>
+        <v>0.4521</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2427</v>
+        <v>-0.2563</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7218</v>
+        <v>0.7083</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1457</v>
+        <v>1.1914</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5385</v>
+        <v>0.5716</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6072</v>
+        <v>0.6198</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6667</v>
+        <v>-0.7393</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7812</v>
+        <v>-0.8278</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1145</v>
+        <v>0.0885</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4084</v>
+        <v>-1.6718</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3512</v>
+        <v>-0.54</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0572</v>
+        <v>-1.1318</v>
       </c>
       <c r="V17" t="n">
-        <v>0.124</v>
+        <v>0.1319</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="18">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8824</v>
+        <v>-1.8936</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1115</v>
+        <v>-0.1083</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7709</v>
+        <v>-1.7853</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4314</v>
+        <v>-0.4369</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1756</v>
+        <v>-0.1778</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2558</v>
+        <v>-0.2591</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.451</v>
+        <v>-0.4567</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2558</v>
+        <v>-0.2591</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,22 +1858,22 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2703</v>
+        <v>-0.2665</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1394</v>
+        <v>-0.1384</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6176</v>
+        <v>-2.3425</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2999</v>
+        <v>-2.038</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3176</v>
+        <v>-0.3045</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4113</v>
+        <v>0.3919</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0227</v>
+        <v>1.0088</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6169</v>
       </c>
       <c r="J19" t="n">
-        <v>0.338</v>
+        <v>0.3552</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9953</v>
+        <v>1.0075</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0733</v>
+        <v>0.0367</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0275</v>
+        <v>0.0013</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0458</v>
+        <v>0.0354</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4769</v>
+        <v>-1.1982</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5895</v>
+        <v>-0.3687</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8874</v>
+        <v>-0.8296</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>H. FIGUEROA ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.066</v>
+        <v>-2.4233</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1288</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1948</v>
+        <v>-3.0569</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1211</v>
+        <v>-0.2265</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5214</v>
+        <v>3.1425</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-3.369</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9388</v>
+        <v>1.1883</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8597</v>
+        <v>4.6813</v>
       </c>
       <c r="L20" t="n">
-        <v>0.079</v>
+        <v>-3.493</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0599</v>
+        <v>-1.4148</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3383</v>
+        <v>-1.5388</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7216</v>
+        <v>0.1239</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4097</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-4.049</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6145</v>
+        <v>1.6196</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1739</v>
+        <v>-2.2797</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0892</v>
+        <v>-0.5782</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0847</v>
+        <v>-1.7015</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.3612</v>
+        <v>2.5123</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6965</v>
+        <v>4.0725</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6647</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6167</v>
+        <v>-3.0773</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8026</v>
+        <v>0.3023</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8141</v>
+        <v>-3.3796</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6231</v>
+        <v>-0.1294</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0425</v>
+        <v>0.5331</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5806</v>
+        <v>-0.6625</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2374</v>
+        <v>1.9753</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5406</v>
+        <v>1.8958</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6968</v>
+        <v>0.0795</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3857</v>
+        <v>-2.1047</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5019</v>
+        <v>-1.3627</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8838</v>
+        <v>-0.742</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4097</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2227</v>
+        <v>-0.1627</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4348</v>
+        <v>0.0275</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6575</v>
+        <v>-0.1902</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1806</v>
+        <v>-2.3804</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1806</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ALVAREZ</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0221</v>
+        <v>-3.5484</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4344</v>
+        <v>-0.894</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5877</v>
+        <v>-2.6544</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2404</v>
+        <v>-2.6376</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1331</v>
+        <v>-1.0474</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3735</v>
+        <v>-1.5902</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0776</v>
+        <v>-1.2261</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6113</v>
+        <v>-0.5341</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.5338</v>
+        <v>-0.6921</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3179</v>
+        <v>-1.4115</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4782</v>
+        <v>-0.5134</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1603</v>
+        <v>-0.8981</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4582</v>
+        <v>0.4049</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.097</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6388</v>
+        <v>0.4049</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.8088</v>
+        <v>-0.1255</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.441</v>
+        <v>0.3321</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.3678</v>
+        <v>-0.4576</v>
       </c>
       <c r="V22" t="n">
-        <v>2.4852</v>
+        <v>-1.1902</v>
       </c>
       <c r="W22" t="n">
-        <v>4.0259</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5407</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7277</v>
+        <v>-6.9151</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6783</v>
+        <v>-3.0476</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0493</v>
+        <v>-3.8676</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4349</v>
+        <v>-1.4847</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8988</v>
+        <v>-1.9353</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3011</v>
+        <v>0.3454</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2812</v>
+        <v>-0.2581</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6036</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.736</v>
+        <v>-1.8301</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6176</v>
+        <v>-1.6772</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1184</v>
+        <v>-0.1529</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2044</v>
+        <v>-1.3759</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1784</v>
+        <v>-0.6717</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.026</v>
+        <v>-0.7043</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4496</v>
+        <v>-2.4349</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2717</v>
+        <v>0.3154</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7213</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.7459</v>
+        <v>-12.3868</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.4473</v>
+        <v>-7.2457</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.2987</v>
+        <v>-5.1411</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.3577</v>
+        <v>-6.397</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.3653</v>
+        <v>-4.3872</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9924</v>
+        <v>-2.0098</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.8923</v>
+        <v>-3.8522</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.2496</v>
+        <v>-3.2234</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6427</v>
+        <v>-0.6288</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4653</v>
+        <v>-2.5448</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1157</v>
+        <v>-1.1638</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3496</v>
+        <v>-1.381</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.475</v>
+        <v>-1.0732</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4822</v>
+        <v>-0.3567</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9928</v>
+        <v>-0.7165</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.0696</v>
+        <v>-3.0945</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.0696</v>
+        <v>-3.0945</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.3013</v>
+        <v>-30.8597</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.238000000000001</v>
+        <v>-4.280899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-27.0633</v>
+        <v>-26.5789</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.535200000000001</v>
+        <v>-6.6731</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2304</v>
+        <v>-2.271299999999998</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.3048</v>
+        <v>-4.402000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>7.097699999999998</v>
+        <v>7.546999999999997</v>
       </c>
       <c r="K25" t="n">
-        <v>8.367000000000001</v>
+        <v>8.6816</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2694</v>
+        <v>-1.1347</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.6328</v>
+        <v>-14.2201</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.5975</v>
+        <v>-10.9527</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.0353</v>
+        <v>-3.2674</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.194000000000001</v>
+        <v>-8.098000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.412</v>
+        <v>-17.2085</v>
       </c>
       <c r="R25" t="n">
-        <v>9.218</v>
+        <v>9.1105</v>
       </c>
       <c r="S25" t="n">
-        <v>-12.047</v>
+        <v>-10.5462</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.8989</v>
+        <v>-2.7359</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.148200000000001</v>
+        <v>-7.8106</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.525200000000001</v>
+        <v>-5.542299999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>7.9753</v>
+        <v>8.116199999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-13.5005</v>
+        <v>-13.6586</v>
       </c>
     </row>
   </sheetData>
